--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,6 +1294,131 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121679582</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6658761</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>121679582</v>
       </c>
       <c r="B7" t="n">
-        <v>57785</v>
+        <v>57793</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>121679582</v>
       </c>
       <c r="B7" t="n">
-        <v>57793</v>
+        <v>57797</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>121679582</v>
       </c>
       <c r="B7" t="n">
-        <v>57797</v>
+        <v>57801</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>121679582</v>
       </c>
       <c r="B7" t="n">
-        <v>57801</v>
+        <v>57803</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>121679582</v>
       </c>
       <c r="B7" t="n">
-        <v>57803</v>
+        <v>57808</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1317,11 +1317,6 @@
       <c r="E7" t="n">
         <v>103001</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Turdus iliacus</t>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>121679582</v>
       </c>
       <c r="B7" t="n">
-        <v>57808</v>
+        <v>57812</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,6 +1316,11 @@
       </c>
       <c r="E7" t="n">
         <v>103001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>123623751</v>
       </c>
       <c r="B8" t="n">
-        <v>86451</v>
+        <v>86466</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>123623751</v>
       </c>
       <c r="B8" t="n">
-        <v>86466</v>
+        <v>86471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 27499-2023 artfynd.xlsx
+++ b/artfynd/A 27499-2023 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>123623751</v>
       </c>
       <c r="B8" t="n">
-        <v>86471</v>
+        <v>86473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
